--- a/edi-redd/data-raw/metadata/feather_redd_survey_site_area_metadata.xlsx
+++ b/edi-redd/data-raw/metadata/feather_redd_survey_site_area_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyvizek/code/hrl/feather-river/edi-redd/data-raw/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BC22F3-EA8E-1E45-A793-F1096CF0A4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF3BB0B-798E-E14E-B436-14FE37094854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67040" yWindow="3060" windowWidth="30560" windowHeight="25740" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46360" yWindow="2120" windowWidth="30560" windowHeight="25740" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attribute" sheetId="9" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t xml:space="preserve">attribute_name </t>
   </si>
@@ -749,6 +749,9 @@
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="L6" s="4">
         <v>52</v>
       </c>
